--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484311_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484311_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9591</v>
+        <v>3.4333</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1924</v>
+        <v>4.8572</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2332</v>
+        <v>-1.4239</v>
       </c>
       <c r="G2" t="n">
         <v>3.2849</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7934</v>
+        <v>0.2676</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8629</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.2601</v>
       </c>
       <c r="V2" t="n">
         <v>1.0529</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALLES OLIVER</t>
+          <t>J. REDA COLL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3256</v>
+        <v>-0.1114</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0398</v>
+        <v>4.8145</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7142</v>
+        <v>-4.926</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2351</v>
+        <v>6.0288</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2773</v>
+        <v>1.3336</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9578</v>
+        <v>4.6952</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8227</v>
+        <v>8.575200000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4597</v>
+        <v>3.0699</v>
       </c>
       <c r="L3" t="n">
-        <v>1.363</v>
+        <v>5.5053</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5876</v>
+        <v>-2.5463</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1824</v>
+        <v>-1.7362</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4052</v>
+        <v>-0.8101</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.5395</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7938</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9053</v>
+        <v>-0.1663</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8884</v>
+        <v>-0.4844</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1638</v>
+        <v>-4.7082</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3824</v>
+        <v>-4.044</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3147</v>
+        <v>-0.1591</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0801</v>
+        <v>0.021</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2345</v>
+        <v>-0.1801</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1686</v>
@@ -766,13 +766,13 @@
         <v>0.1953</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2196</v>
+        <v>-0.064</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0985</v>
+        <v>-0.044</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1219</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3634</v>
+        <v>-0.3924</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8269</v>
+        <v>0.9885</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1903</v>
+        <v>-1.3809</v>
       </c>
       <c r="G5" t="n">
         <v>2.0776</v>
@@ -844,13 +844,13 @@
         <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8688</v>
+        <v>0.8398</v>
       </c>
       <c r="T5" t="n">
-        <v>0.399</v>
+        <v>0.5607</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4698</v>
+        <v>0.2791</v>
       </c>
       <c r="V5" t="n">
         <v>0.011</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. TABERNER PERALTA</t>
+          <t>J. VALLES OLIVER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.7398</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0605</v>
+        <v>1.6553</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-2.3951</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0698</v>
+        <v>2.2351</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0698</v>
+        <v>1.2773</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.9578</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3.8227</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.4597</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.363</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0698</v>
+        <v>-1.5876</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0698</v>
+        <v>-1.1824</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.4052</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1953</v>
+        <v>0.7284</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0605</v>
+        <v>0.5208</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1348</v>
+        <v>0.2075</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6093</v>
+        <v>-1.1638</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6093</v>
+        <v>-2.3824</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. REDA COLL</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.281</v>
+        <v>-0.769</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0263</v>
+        <v>1.1301</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.3073</v>
+        <v>-1.8992</v>
       </c>
       <c r="G7" t="n">
-        <v>6.0288</v>
+        <v>-0.3431</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3336</v>
+        <v>-3.472</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6952</v>
+        <v>3.1289</v>
       </c>
       <c r="J7" t="n">
-        <v>8.575200000000001</v>
+        <v>2.8172</v>
       </c>
       <c r="K7" t="n">
-        <v>3.0699</v>
+        <v>-1.1218</v>
       </c>
       <c r="L7" t="n">
-        <v>5.5053</v>
+        <v>3.939</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5463</v>
+        <v>-3.1603</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7362</v>
+        <v>-2.3502</v>
       </c>
       <c r="O7" t="n">
         <v>-0.8101</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8203</v>
+        <v>0.0757</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9546</v>
+        <v>-0.0108</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8657</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.7082</v>
+        <v>-0.1109</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.044</v>
+        <v>-0.3881</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. PONS AVECILLAS</t>
+          <t>P. TABERNER PERALTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2926</v>
+        <v>-0.7734</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5494</v>
+        <v>0.0406</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2568</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2425</v>
+        <v>-0.0698</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5682</v>
+        <v>-0.0698</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6743</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3073</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6332</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0648</v>
+        <v>-0.0698</v>
       </c>
       <c r="N8" t="n">
-        <v>0.065</v>
+        <v>-0.0698</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2454</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2421</v>
+        <v>0.0406</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0033</v>
+        <v>-0.1348</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>S. PONS AVECILLAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9381</v>
+        <v>-1.1854</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2607</v>
+        <v>-1.3877</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1988</v>
+        <v>0.2023</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3431</v>
+        <v>-1.2425</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.472</v>
+        <v>-0.5682</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1289</v>
+        <v>-0.6743</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8172</v>
+        <v>-1.3073</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1218</v>
+        <v>-0.6332</v>
       </c>
       <c r="L9" t="n">
-        <v>3.939</v>
+        <v>-0.6741</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1603</v>
+        <v>0.0648</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.3502</v>
+        <v>0.065</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8101</v>
+        <v>-0.0002</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0934</v>
+        <v>-0.1383</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8803</v>
+        <v>-0.0805</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2131</v>
+        <v>-0.0578</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1109</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6112</v>
+        <v>-2.4883</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3028</v>
+        <v>-0.3434</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3084</v>
+        <v>-2.145</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1583</v>
@@ -1234,13 +1234,13 @@
         <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2383</v>
+        <v>0.3612</v>
       </c>
       <c r="T10" t="n">
-        <v>0.399</v>
+        <v>0.3584</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1607</v>
+        <v>0.0027</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3245</v>
+        <v>-3.8845</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9517</v>
+        <v>-2.7295</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3729</v>
+        <v>-1.155</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3735</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1574</v>
+        <v>0.2827</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1102</v>
+        <v>0.3324</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2676</v>
+        <v>-0.0497</v>
       </c>
       <c r="V11" t="n">
         <v>0.011</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.960000000000001</v>
+        <v>-8.6972</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.0658</v>
+        <v>-6.803</v>
       </c>
       <c r="F12" t="n">
         <v>-1.8942</v>
@@ -1390,10 +1390,10 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6603</v>
+        <v>-0.3976</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5915</v>
+        <v>-0.3287</v>
       </c>
       <c r="U12" t="n">
         <v>-0.0689</v>
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.6753</v>
+        <v>-15.7672</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3358</v>
+        <v>2.2436</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.011</v>
+        <v>-18.0111</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1408000000000023</v>
+        <v>-0.1408000000000005</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.886600000000001</v>
+        <v>-6.8866</v>
       </c>
       <c r="I13" t="n">
-        <v>6.7459</v>
+        <v>6.745899999999998</v>
       </c>
       <c r="J13" t="n">
         <v>16.7327</v>
       </c>
       <c r="K13" t="n">
-        <v>7.2844</v>
+        <v>7.284400000000002</v>
       </c>
       <c r="L13" t="n">
         <v>9.4483</v>
@@ -1468,10 +1468,10 @@
         <v>10.7438</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3025999999999996</v>
+        <v>1.2106</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8264000000000001</v>
+        <v>1.7344</v>
       </c>
       <c r="U13" t="n">
         <v>-0.5238999999999999</v>
@@ -1480,7 +1480,7 @@
         <v>-6.0931</v>
       </c>
       <c r="W13" t="n">
-        <v>5.264299999999999</v>
+        <v>5.2643</v>
       </c>
       <c r="X13" t="n">
         <v>-11.3577</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8385</v>
+        <v>7.3441</v>
       </c>
       <c r="E14" t="n">
-        <v>8.2714</v>
+        <v>4.9524</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4329</v>
+        <v>2.3918</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6909</v>
+        <v>2.7451</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6646</v>
+        <v>3.4058</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0263</v>
+        <v>-0.6607</v>
       </c>
       <c r="J14" t="n">
-        <v>3.283</v>
+        <v>3.7936</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9071</v>
+        <v>4.5881</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3758</v>
+        <v>-0.7945</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.5921</v>
+        <v>-1.0485</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2425</v>
+        <v>-1.1824</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3496</v>
+        <v>0.1338</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>3.1255</v>
       </c>
       <c r="S14" t="n">
-        <v>4.6202</v>
+        <v>-0.1741</v>
       </c>
       <c r="T14" t="n">
-        <v>4.8013</v>
+        <v>-0.4889</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1812</v>
+        <v>0.3148</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5507</v>
+        <v>3.601</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1638</v>
+        <v>3.601</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9386</v>
+        <v>4.8932</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2446</v>
+        <v>5.1368</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6941</v>
+        <v>-0.2436</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7451</v>
+        <v>0.6909</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4058</v>
+        <v>0.6646</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6607</v>
+        <v>0.0263</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7936</v>
+        <v>3.283</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5881</v>
+        <v>1.9071</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7945</v>
+        <v>1.3758</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0485</v>
+        <v>-2.5921</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1824</v>
+        <v>-1.2425</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1338</v>
+        <v>-1.3496</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1255</v>
+        <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5796</v>
+        <v>1.6749</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1967</v>
+        <v>1.6668</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6171</v>
+        <v>0.0081</v>
       </c>
       <c r="V15" t="n">
-        <v>3.601</v>
+        <v>1.5507</v>
       </c>
       <c r="W15" t="n">
-        <v>3.601</v>
+        <v>1.1638</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="16">
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3206</v>
+        <v>4.5228</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9329</v>
+        <v>6.1352</v>
       </c>
       <c r="F16" t="n">
         <v>-1.6123</v>
@@ -1702,10 +1702,10 @@
         <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4045</v>
+        <v>0.6067</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.2849</v>
       </c>
       <c r="U16" t="n">
         <v>0.3218</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5213</v>
+        <v>3.4157</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9035</v>
+        <v>1.6113</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6178</v>
+        <v>1.8044</v>
       </c>
       <c r="G17" t="n">
         <v>1.1865</v>
@@ -1780,13 +1780,13 @@
         <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0093</v>
+        <v>-0.1149</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7125</v>
+        <v>-0.0047</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2968</v>
+        <v>-0.1102</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. DI BONAVENTURA</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4636</v>
+        <v>1.6865</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6807</v>
+        <v>1.3766</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2171</v>
+        <v>0.31</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5219</v>
+        <v>1.43</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0425</v>
+        <v>0.3106</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5643</v>
+        <v>1.1194</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3951</v>
+        <v>1.2954</v>
       </c>
       <c r="K18" t="n">
-        <v>1.801</v>
+        <v>0.0409</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5942</v>
+        <v>1.2544</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.917</v>
+        <v>0.1346</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7585</v>
+        <v>0.2696</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1585</v>
+        <v>-0.135</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3093</v>
+        <v>0.1431</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0083</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3009</v>
+        <v>0.0619</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>G. DI BONAVENTURA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4026</v>
+        <v>1.4715</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1743</v>
+        <v>2.5796</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2282</v>
+        <v>-1.1082</v>
       </c>
       <c r="G19" t="n">
-        <v>1.43</v>
+        <v>-0.5219</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3106</v>
+        <v>1.0425</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1194</v>
+        <v>-1.5643</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2954</v>
+        <v>2.3951</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0409</v>
+        <v>1.801</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2544</v>
+        <v>0.5942</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1346</v>
+        <v>-2.917</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2696</v>
+        <v>-0.7585</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.135</v>
+        <v>-2.1585</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1409</v>
+        <v>0.3171</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.121</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0198</v>
+        <v>0.4099</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5131</v>
+        <v>0.2959</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1594</v>
+        <v>-0.7549</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6463</v>
+        <v>1.0508</v>
       </c>
       <c r="G20" t="n">
         <v>0.7255</v>
@@ -2014,13 +2014,13 @@
         <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2739</v>
+        <v>-0.465</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.3218</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5476</v>
+        <v>-0.1432</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9414</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3061</v>
+        <v>-0.3749</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2771</v>
+        <v>-1.4429</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5832</v>
+        <v>1.068</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9322</v>
+        <v>-2.1157</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2371</v>
+        <v>0.6359</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1694</v>
+        <v>-2.7517</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5797</v>
+        <v>0.0118</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5116000000000001</v>
+        <v>1.9531</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06809999999999999</v>
+        <v>-1.9414</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.512</v>
+        <v>-2.1275</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2745</v>
+        <v>-1.3172</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.2375</v>
+        <v>-0.8103</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>3.3208</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0501</v>
+        <v>-0.5131</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3026</v>
+        <v>-0.3878</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2525</v>
+        <v>-0.1253</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5519</v>
+        <v>-0.8213</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0583</v>
+        <v>0.6816</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4936</v>
+        <v>-1.5029</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3375</v>
+        <v>-2.9322</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5526</v>
+        <v>0.2371</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.89</v>
+        <v>-3.1694</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0162</v>
+        <v>0.5797</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9619</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0543</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3536</v>
+        <v>-3.512</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4093</v>
+        <v>-0.2745</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9443</v>
+        <v>-3.2375</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0424</v>
+        <v>0.4347</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.121</v>
+        <v>0.1018</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.3329</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9423</v>
+        <v>-1.4235</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2518</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3095</v>
+        <v>-0.4664</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1157</v>
+        <v>-0.3375</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6359</v>
+        <v>0.5526</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7517</v>
+        <v>-0.89</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0118</v>
+        <v>1.0162</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9531</v>
+        <v>0.9619</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9414</v>
+        <v>0.0543</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1275</v>
+        <v>-1.3536</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3172</v>
+        <v>-0.4093</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8103</v>
+        <v>-0.9443</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3674</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3208</v>
+        <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0805</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1967</v>
+        <v>-0.0199</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8838</v>
+        <v>0.1059</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4968</v>
+        <v>-2.3126</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2228</v>
+        <v>-2.5261</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.274</v>
+        <v>0.2135</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0954</v>
@@ -2326,13 +2326,13 @@
         <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.46</v>
+        <v>-0.2758</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0083</v>
+        <v>-0.295</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4683</v>
+        <v>0.0192</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5507</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.675</v>
+        <v>18.6974</v>
       </c>
       <c r="E25" t="n">
-        <v>16.7922</v>
+        <v>16.7924</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1172</v>
+        <v>1.9051</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1407000000000004</v>
+        <v>0.1406999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>6.886699999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-6.7459</v>
+        <v>-6.745900000000002</v>
       </c>
       <c r="J25" t="n">
         <v>16.8734</v>
@@ -2392,7 +2392,7 @@
         <v>-7.2845</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.448399999999999</v>
+        <v>-9.448400000000001</v>
       </c>
       <c r="P25" t="n">
         <v>10.7438</v>
@@ -2404,13 +2404,13 @@
         <v>21.4876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3027000000000002</v>
+        <v>1.7196</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5237000000000003</v>
+        <v>0.5238</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8265</v>
+        <v>1.1958</v>
       </c>
       <c r="V25" t="n">
         <v>6.0932</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484311_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484311_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1109</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-4.044</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1219</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2077</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.3824</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3881</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1250,6 +1295,11 @@
       </c>
       <c r="X10" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.2663</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7312</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,11 +1545,12 @@
       <c r="X13" t="n">
         <v>-11.3577</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,31 +1562,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.3441</v>
+        <v>6.4301</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9524</v>
+        <v>4.0384</v>
       </c>
       <c r="F14" t="n">
         <v>2.3918</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7451</v>
+        <v>1.8311</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4058</v>
+        <v>3.0988</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6607</v>
+        <v>-1.2677</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7936</v>
+        <v>2.8797</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5881</v>
+        <v>4.2811</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7945</v>
+        <v>-1.4015</v>
       </c>
       <c r="M14" t="n">
         <v>-1.0485</v>
@@ -1562,6 +1623,11 @@
       </c>
       <c r="X14" t="n">
         <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,11 +1790,16 @@
       <c r="X16" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,31 +1811,31 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4157</v>
+        <v>2.5018</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6113</v>
+        <v>0.6974</v>
       </c>
       <c r="F17" t="n">
         <v>1.8044</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1865</v>
+        <v>0.2725</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.5564</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3231</v>
+        <v>-0.2839</v>
       </c>
       <c r="J17" t="n">
-        <v>1.616</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5617</v>
+        <v>1.2548</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0543</v>
+        <v>-0.5527</v>
       </c>
       <c r="M17" t="n">
         <v>-0.4295</v>
@@ -1796,12 +1872,17 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1874,6 +1955,11 @@
       </c>
       <c r="X18" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1953,11 +2039,16 @@
       <c r="X19" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2959</v>
+        <v>0.914</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7549</v>
+        <v>0.914</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0508</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7255</v>
+        <v>0.914</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0497</v>
+        <v>0.307</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3241</v>
+        <v>0.607</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2664</v>
+        <v>0.914</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8596</v>
+        <v>0.307</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4591</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1901</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.465</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3218</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1432</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3749</v>
+        <v>0.914</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4429</v>
+        <v>0.914</v>
       </c>
       <c r="F21" t="n">
-        <v>1.068</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1157</v>
+        <v>0.914</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6359</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7517</v>
+        <v>0.607</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0118</v>
+        <v>0.914</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9531</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9414</v>
+        <v>0.607</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1275</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3172</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8103</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.3208</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5131</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3878</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1253</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8213</v>
+        <v>0.2959</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6816</v>
+        <v>-0.7549</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5029</v>
+        <v>1.0508</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9322</v>
+        <v>0.7255</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2371</v>
+        <v>1.0497</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.1694</v>
+        <v>-0.3241</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5797</v>
+        <v>0.2664</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.8596</v>
       </c>
       <c r="L22" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.512</v>
+        <v>0.4591</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2745</v>
+        <v>0.1901</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.2375</v>
+        <v>0.269</v>
       </c>
       <c r="P22" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
         <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4347</v>
+        <v>-0.465</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1018</v>
+        <v>-0.3218</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3329</v>
+        <v>-0.1432</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4235</v>
+        <v>-0.3749</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-1.4429</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4664</v>
+        <v>1.068</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3375</v>
+        <v>-2.1157</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5526</v>
+        <v>0.6359</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.89</v>
+        <v>-2.7517</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0162</v>
+        <v>0.0118</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9619</v>
+        <v>1.9531</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0543</v>
+        <v>-1.9414</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3536</v>
+        <v>-2.1275</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4093</v>
+        <v>-1.3172</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9443</v>
+        <v>-0.8103</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>3.3208</v>
       </c>
       <c r="S23" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.5131</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0199</v>
+        <v>-0.3878</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1059</v>
+        <v>-0.1253</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3126</v>
+        <v>-0.8213</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5261</v>
+        <v>0.6816</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2135</v>
+        <v>-1.5029</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0954</v>
+        <v>-2.9322</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4168</v>
+        <v>0.2371</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3214</v>
+        <v>-3.1694</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5548999999999999</v>
+        <v>0.5797</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2024</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6475</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4595</v>
+        <v>-3.512</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2144</v>
+        <v>-0.2745</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6739000000000001</v>
+        <v>-3.2375</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2758</v>
+        <v>0.4347</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.295</v>
+        <v>0.1018</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0192</v>
+        <v>0.3329</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.5507</v>
+        <v>-0.2772</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.8279</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,235 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.6974</v>
+        <v>-1.4235</v>
       </c>
       <c r="E25" t="n">
-        <v>16.7924</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="F25" t="n">
+        <v>-0.4664</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.3375</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5526</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.0162</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.9619</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.3536</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.4093</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.9443</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.0199</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>U. FERNANDEZ RUIZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.3126</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2.5261</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.2135</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.0954</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.4168</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.3214</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.5548999999999999</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.2024</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4595</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.2144</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.6739000000000001</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2758</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.295</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.5507</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484311_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>18.6975</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.7925</v>
+      </c>
+      <c r="F27" t="n">
         <v>1.9051</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.1406999999999999</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="G27" t="n">
+        <v>0.1407000000000003</v>
+      </c>
+      <c r="H27" t="n">
         <v>6.886699999999999</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I27" t="n">
         <v>-6.745900000000002</v>
       </c>
-      <c r="J25" t="n">
-        <v>16.8734</v>
-      </c>
-      <c r="K25" t="n">
-        <v>14.1709</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2.702299999999999</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="J27" t="n">
+        <v>16.8736</v>
+      </c>
+      <c r="K27" t="n">
+        <v>14.171</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.7023</v>
+      </c>
+      <c r="M27" t="n">
         <v>-16.7327</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>-7.2845</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>-9.448400000000001</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P27" t="n">
         <v>10.7438</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
         <v>-10.7437</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>21.4876</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S27" t="n">
         <v>1.7196</v>
       </c>
-      <c r="T25" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="T27" t="n">
+        <v>0.5238000000000003</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.1958</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V27" t="n">
         <v>6.0932</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>10.1388</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>-4.0457</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
